--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/40.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/40.xlsx
@@ -426,13 +426,13 @@
         <v>-10.7117508458377</v>
       </c>
       <c r="E2">
-        <v>-11.35582539356817</v>
+        <v>-16.04016947658254</v>
       </c>
       <c r="F2">
-        <v>-3.751736585346873</v>
+        <v>-3.908162172221921</v>
       </c>
       <c r="G2">
-        <v>-8.497638552145649</v>
+        <v>-10.33455433442997</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.15215194867428</v>
       </c>
       <c r="E3">
-        <v>-12.10804115403427</v>
+        <v>-16.43578149436663</v>
       </c>
       <c r="F3">
-        <v>-3.474981521173766</v>
+        <v>-3.859666230992426</v>
       </c>
       <c r="G3">
-        <v>-8.396683465925573</v>
+        <v>-10.89657571899543</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.569915100283062</v>
       </c>
       <c r="E4">
-        <v>-13.1246428124902</v>
+        <v>-15.30381243209129</v>
       </c>
       <c r="F4">
-        <v>-3.237097597377027</v>
+        <v>-4.120736986760927</v>
       </c>
       <c r="G4">
-        <v>-8.484687697996019</v>
+        <v>-10.20862449266164</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.019739232825408</v>
       </c>
       <c r="E5">
-        <v>-12.94446841714702</v>
+        <v>-16.71486681898534</v>
       </c>
       <c r="F5">
-        <v>-3.283223579467112</v>
+        <v>-3.799173044668187</v>
       </c>
       <c r="G5">
-        <v>-8.147975421742286</v>
+        <v>-9.526390578474169</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.509350638984699</v>
       </c>
       <c r="E6">
-        <v>-13.46479008062834</v>
+        <v>-17.49414021164728</v>
       </c>
       <c r="F6">
-        <v>-3.239741746126763</v>
+        <v>-3.841155533009469</v>
       </c>
       <c r="G6">
-        <v>-7.581716538886567</v>
+        <v>-9.791340159073121</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.042098727666273</v>
       </c>
       <c r="E7">
-        <v>-14.47807236763665</v>
+        <v>-17.8104767634531</v>
       </c>
       <c r="F7">
-        <v>-3.446450891086546</v>
+        <v>-3.683745845659895</v>
       </c>
       <c r="G7">
-        <v>-7.78011753305509</v>
+        <v>-9.369659421008453</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.631392389205502</v>
       </c>
       <c r="E8">
-        <v>-16.0024201172546</v>
+        <v>-18.17542195525724</v>
       </c>
       <c r="F8">
-        <v>-3.221727240218082</v>
+        <v>-3.984806037798542</v>
       </c>
       <c r="G8">
-        <v>-7.280172187896512</v>
+        <v>-9.203340923661008</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.268017764483351</v>
       </c>
       <c r="E9">
-        <v>-16.02892074714748</v>
+        <v>-19.28297801415723</v>
       </c>
       <c r="F9">
-        <v>-3.345753721234835</v>
+        <v>-3.704425209503382</v>
       </c>
       <c r="G9">
-        <v>-7.135627148560854</v>
+        <v>-8.631831515580005</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.958757646487767</v>
       </c>
       <c r="E10">
-        <v>-15.86629871705803</v>
+        <v>-19.75768435895929</v>
       </c>
       <c r="F10">
-        <v>-3.387585446708808</v>
+        <v>-3.65809876250182</v>
       </c>
       <c r="G10">
-        <v>-7.305113837989381</v>
+        <v>-8.850887003368042</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.684917248406332</v>
       </c>
       <c r="E11">
-        <v>-16.93516349403648</v>
+        <v>-19.92484392000442</v>
       </c>
       <c r="F11">
-        <v>-3.108658403205561</v>
+        <v>-3.87345026457501</v>
       </c>
       <c r="G11">
-        <v>-6.677427782652486</v>
+        <v>-8.543118826764156</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.448008222753195</v>
       </c>
       <c r="E12">
-        <v>-17.67414252497817</v>
+        <v>-19.8268251001084</v>
       </c>
       <c r="F12">
-        <v>-3.39134706308492</v>
+        <v>-3.622912200333105</v>
       </c>
       <c r="G12">
-        <v>-6.030593531916446</v>
+        <v>-8.24285234635226</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.225382742884121</v>
       </c>
       <c r="E13">
-        <v>-17.98566078043982</v>
+        <v>-21.37865163000489</v>
       </c>
       <c r="F13">
-        <v>-3.282579109627734</v>
+        <v>-3.775802315133004</v>
       </c>
       <c r="G13">
-        <v>-5.768126860471948</v>
+        <v>-7.76176717913091</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.016545635108224</v>
       </c>
       <c r="E14">
-        <v>-19.13893178444724</v>
+        <v>-20.98962854190196</v>
       </c>
       <c r="F14">
-        <v>-2.951148483400249</v>
+        <v>-3.460842117975382</v>
       </c>
       <c r="G14">
-        <v>-5.553550540798546</v>
+        <v>-6.459530985803196</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.799329949619434</v>
       </c>
       <c r="E15">
-        <v>-19.64895569803512</v>
+        <v>-21.94189869860492</v>
       </c>
       <c r="F15">
-        <v>-3.239076567102315</v>
+        <v>-3.295824704398498</v>
       </c>
       <c r="G15">
-        <v>-4.876073880551012</v>
+        <v>-6.874077498230734</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.576698811485779</v>
       </c>
       <c r="E16">
-        <v>-19.83232719602772</v>
+        <v>-22.2310553494167</v>
       </c>
       <c r="F16">
-        <v>-2.720267577626776</v>
+        <v>-3.345182976094307</v>
       </c>
       <c r="G16">
-        <v>-4.627107613815662</v>
+        <v>-6.930386567308197</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.337665124071562</v>
       </c>
       <c r="E17">
-        <v>-21.03176146406933</v>
+        <v>-24.07735495860997</v>
       </c>
       <c r="F17">
-        <v>-2.427693181162408</v>
+        <v>-3.076417515521201</v>
       </c>
       <c r="G17">
-        <v>-4.180183966014051</v>
+        <v>-5.987867631186612</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.096721016396674</v>
       </c>
       <c r="E18">
-        <v>-22.14218404701617</v>
+        <v>-23.77925910010705</v>
       </c>
       <c r="F18">
-        <v>-2.092377511815793</v>
+        <v>-2.960827956501961</v>
       </c>
       <c r="G18">
-        <v>-3.551610684472631</v>
+        <v>-6.206853597518323</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.856360439669634</v>
       </c>
       <c r="E19">
-        <v>-22.10977375854327</v>
+        <v>-24.86124286628572</v>
       </c>
       <c r="F19">
-        <v>-1.989892725108841</v>
+        <v>-2.73179099656712</v>
       </c>
       <c r="G19">
-        <v>-2.904448689728203</v>
+        <v>-5.512317696106924</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.640408042648612</v>
       </c>
       <c r="E20">
-        <v>-23.16658826618731</v>
+        <v>-25.86528253784438</v>
       </c>
       <c r="F20">
-        <v>-1.952713939336393</v>
+        <v>-2.329406560452843</v>
       </c>
       <c r="G20">
-        <v>-3.317813337398221</v>
+        <v>-6.181421986685641</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.458116215322972</v>
       </c>
       <c r="E21">
-        <v>-24.41178729255044</v>
+        <v>-26.35837901559158</v>
       </c>
       <c r="F21">
-        <v>-1.63103651090947</v>
+        <v>-2.359907048223921</v>
       </c>
       <c r="G21">
-        <v>-3.23405653525466</v>
+        <v>-5.958367359886166</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.332542825196372</v>
       </c>
       <c r="E22">
-        <v>-24.59772643530538</v>
+        <v>-25.87404966352322</v>
       </c>
       <c r="F22">
-        <v>-1.568118693197236</v>
+        <v>-1.904545203231005</v>
       </c>
       <c r="G22">
-        <v>-3.108404779311622</v>
+        <v>-5.572169048911407</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.267775741893902</v>
       </c>
       <c r="E23">
-        <v>-23.67172595632092</v>
+        <v>-27.10728446155808</v>
       </c>
       <c r="F23">
-        <v>-1.158359302095836</v>
+        <v>-1.558498862548526</v>
       </c>
       <c r="G23">
-        <v>-3.899224587187184</v>
+        <v>-6.001679227176451</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.276269253229203</v>
       </c>
       <c r="E24">
-        <v>-24.76018091185655</v>
+        <v>-27.3816420593128</v>
       </c>
       <c r="F24">
-        <v>-0.8255494441426895</v>
+        <v>-1.24134514850829</v>
       </c>
       <c r="G24">
-        <v>-3.577903037145523</v>
+        <v>-6.125586325620293</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.350205417534724</v>
       </c>
       <c r="E25">
-        <v>-25.02616536117107</v>
+        <v>-27.64251838994667</v>
       </c>
       <c r="F25">
-        <v>-0.8451411615863006</v>
+        <v>-1.446235198651525</v>
       </c>
       <c r="G25">
-        <v>-3.415739274449863</v>
+        <v>-5.702743586071342</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.487042735916901</v>
       </c>
       <c r="E26">
-        <v>-25.09874774256602</v>
+        <v>-28.44926603441314</v>
       </c>
       <c r="F26">
-        <v>-0.6607929662976874</v>
+        <v>-1.201031820483649</v>
       </c>
       <c r="G26">
-        <v>-4.003913968775556</v>
+        <v>-6.238244190321692</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.665021207127539</v>
       </c>
       <c r="E27">
-        <v>-25.44597301557815</v>
+        <v>-28.51455304418172</v>
       </c>
       <c r="F27">
-        <v>-0.5243782507720676</v>
+        <v>-1.311748922439623</v>
       </c>
       <c r="G27">
-        <v>-4.114482879241676</v>
+        <v>-5.93572984948863</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.867982465648276</v>
       </c>
       <c r="E28">
-        <v>-25.32120902819282</v>
+        <v>-27.53339122330983</v>
       </c>
       <c r="F28">
-        <v>-0.4117964937923924</v>
+        <v>-1.357231263057733</v>
       </c>
       <c r="G28">
-        <v>-4.139318591877288</v>
+        <v>-6.441048210057445</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.067412388550303</v>
       </c>
       <c r="E29">
-        <v>-25.28111391932891</v>
+        <v>-27.75485624465495</v>
       </c>
       <c r="F29">
-        <v>-0.5286766492251942</v>
+        <v>-1.291212037789418</v>
       </c>
       <c r="G29">
-        <v>-4.156377833041152</v>
+        <v>-6.951372115481638</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.244931026919809</v>
       </c>
       <c r="E30">
-        <v>-24.74259231881075</v>
+        <v>-27.39080769070432</v>
       </c>
       <c r="F30">
-        <v>-0.4095855811943205</v>
+        <v>-1.082496586980054</v>
       </c>
       <c r="G30">
-        <v>-5.204350886770682</v>
+        <v>-7.087127656410531</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.376698203272146</v>
       </c>
       <c r="E31">
-        <v>-24.17858899505144</v>
+        <v>-27.21832717270017</v>
       </c>
       <c r="F31">
-        <v>-0.4899670404923733</v>
+        <v>-1.027078807732767</v>
       </c>
       <c r="G31">
-        <v>-4.654383198513717</v>
+        <v>-6.897923357750104</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.452219802731419</v>
       </c>
       <c r="E32">
-        <v>-24.26344354100717</v>
+        <v>-26.98996075696736</v>
       </c>
       <c r="F32">
-        <v>-0.2133751646976184</v>
+        <v>-1.534872995853281</v>
       </c>
       <c r="G32">
-        <v>-4.973059622669501</v>
+        <v>-7.34895539256595</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.461081762821254</v>
       </c>
       <c r="E33">
-        <v>-23.6148030380445</v>
+        <v>-27.14970267758793</v>
       </c>
       <c r="F33">
-        <v>-0.6307894989682893</v>
+        <v>-1.302892018168891</v>
       </c>
       <c r="G33">
-        <v>-4.834771514403065</v>
+        <v>-7.360578717954331</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.406605128921642</v>
       </c>
       <c r="E34">
-        <v>-23.22358364004785</v>
+        <v>-26.10151491292851</v>
       </c>
       <c r="F34">
-        <v>-0.4475256366099407</v>
+        <v>-1.036026004050405</v>
       </c>
       <c r="G34">
-        <v>-5.011591062201078</v>
+        <v>-7.30480264670869</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.292261797453018</v>
       </c>
       <c r="E35">
-        <v>-22.97310468573558</v>
+        <v>-26.99049511690027</v>
       </c>
       <c r="F35">
-        <v>-0.6028279572867919</v>
+        <v>-1.139788961659876</v>
       </c>
       <c r="G35">
-        <v>-5.154719188045928</v>
+        <v>-7.204721544510982</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.132694041792848</v>
       </c>
       <c r="E36">
-        <v>-22.70700702457087</v>
+        <v>-25.74954832763034</v>
       </c>
       <c r="F36">
-        <v>-0.5788574897519827</v>
+        <v>-1.334406427640995</v>
       </c>
       <c r="G36">
-        <v>-5.0098563363385</v>
+        <v>-7.066549305338421</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.940651796264468</v>
       </c>
       <c r="E37">
-        <v>-22.35580575138</v>
+        <v>-24.79024092231946</v>
       </c>
       <c r="F37">
-        <v>-0.6314422524816953</v>
+        <v>-1.131655222131788</v>
       </c>
       <c r="G37">
-        <v>-4.815606766276224</v>
+        <v>-7.246407933941486</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.736416664435299</v>
       </c>
       <c r="E38">
-        <v>-22.42942968179671</v>
+        <v>-25.21698167043228</v>
       </c>
       <c r="F38">
-        <v>-0.3634173523666929</v>
+        <v>-1.204493567859948</v>
       </c>
       <c r="G38">
-        <v>-4.72773164548181</v>
+        <v>-7.027590805432278</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.535291790914894</v>
       </c>
       <c r="E39">
-        <v>-21.63413001962162</v>
+        <v>-24.64495389073138</v>
       </c>
       <c r="F39">
-        <v>-0.5991558045901818</v>
+        <v>-1.336149312656485</v>
       </c>
       <c r="G39">
-        <v>-4.876875032571515</v>
+        <v>-6.641064750449131</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.356034312744026</v>
       </c>
       <c r="E40">
-        <v>-20.79381732581029</v>
+        <v>-23.40329160256824</v>
       </c>
       <c r="F40">
-        <v>-0.6808560247934914</v>
+        <v>-1.512130997176823</v>
       </c>
       <c r="G40">
-        <v>-4.750494956609838</v>
+        <v>-6.43443705061552</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.209281417674172</v>
       </c>
       <c r="E41">
-        <v>-20.43031671721459</v>
+        <v>-23.68462305029476</v>
       </c>
       <c r="F41">
-        <v>-0.9001778918282997</v>
+        <v>-1.423096411989127</v>
       </c>
       <c r="G41">
-        <v>-4.752229682472416</v>
+        <v>-6.758042877079278</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.105987087769909</v>
       </c>
       <c r="E42">
-        <v>-20.62524940934878</v>
+        <v>-23.27771701833554</v>
       </c>
       <c r="F42">
-        <v>-0.738184019271634</v>
+        <v>-1.519922620967555</v>
       </c>
       <c r="G42">
-        <v>-4.654015727958858</v>
+        <v>-7.037727695873526</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.047950899980518</v>
       </c>
       <c r="E43">
-        <v>-20.09760067492304</v>
+        <v>-22.39006818572204</v>
       </c>
       <c r="F43">
-        <v>-0.9611606432875938</v>
+        <v>-1.76434153520498</v>
       </c>
       <c r="G43">
-        <v>-4.689988115788578</v>
+        <v>-6.303412279262245</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.036515948904799</v>
       </c>
       <c r="E44">
-        <v>-18.75825467394045</v>
+        <v>-21.68157937027399</v>
       </c>
       <c r="F44">
-        <v>-0.822894526616717</v>
+        <v>-1.892179334642014</v>
       </c>
       <c r="G44">
-        <v>-4.239621500626126</v>
+        <v>-6.277394701869112</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.065301019829959</v>
       </c>
       <c r="E45">
-        <v>-18.41015540544483</v>
+        <v>-22.32585895276728</v>
       </c>
       <c r="F45">
-        <v>-0.8059196217985496</v>
+        <v>-1.791731503378546</v>
       </c>
       <c r="G45">
-        <v>-4.506037652898975</v>
+        <v>-5.853701152116568</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.128159519988476</v>
       </c>
       <c r="E46">
-        <v>-18.97157749901977</v>
+        <v>-20.44392931008165</v>
       </c>
       <c r="F46">
-        <v>-1.514973954103231</v>
+        <v>-1.764904825038884</v>
       </c>
       <c r="G46">
-        <v>-4.375992803025325</v>
+        <v>-5.877192783263236</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.214160860479557</v>
       </c>
       <c r="E47">
-        <v>-17.46682898490702</v>
+        <v>-21.05270112788079</v>
       </c>
       <c r="F47">
-        <v>-1.281435645701578</v>
+        <v>-1.776612141542649</v>
       </c>
       <c r="G47">
-        <v>-3.71723065671129</v>
+        <v>-5.954272215054088</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.314578199058835</v>
       </c>
       <c r="E48">
-        <v>-16.95832663858572</v>
+        <v>-20.81577589627349</v>
       </c>
       <c r="F48">
-        <v>-1.105721523852344</v>
+        <v>-1.936911174393187</v>
       </c>
       <c r="G48">
-        <v>-4.525768504313032</v>
+        <v>-5.820016351254484</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.419535301325568</v>
       </c>
       <c r="E49">
-        <v>-16.70807410797384</v>
+        <v>-20.24504778861279</v>
       </c>
       <c r="F49">
-        <v>-1.375225059781343</v>
+        <v>-1.973216860923084</v>
       </c>
       <c r="G49">
-        <v>-4.345585442247119</v>
+        <v>-5.957748287870323</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.523013754209241</v>
       </c>
       <c r="E50">
-        <v>-16.3483910029666</v>
+        <v>-19.65501932473139</v>
       </c>
       <c r="F50">
-        <v>-1.69803072461088</v>
+        <v>-2.139713738681368</v>
       </c>
       <c r="G50">
-        <v>-3.558311228644116</v>
+        <v>-6.546101751655137</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.620100536075036</v>
       </c>
       <c r="E51">
-        <v>-15.96411375562371</v>
+        <v>-18.43613526082684</v>
       </c>
       <c r="F51">
-        <v>-1.510036056015143</v>
+        <v>-1.906168803340492</v>
       </c>
       <c r="G51">
-        <v>-4.235205232876738</v>
+        <v>-6.304474964380351</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.709620687953031</v>
       </c>
       <c r="E52">
-        <v>-15.8073560993742</v>
+        <v>-19.15388027714656</v>
       </c>
       <c r="F52">
-        <v>-1.474421227899181</v>
+        <v>-1.909387839067771</v>
       </c>
       <c r="G52">
-        <v>-4.323623283139593</v>
+        <v>-6.046355039228915</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.792249107906462</v>
       </c>
       <c r="E53">
-        <v>-15.36164557364325</v>
+        <v>-18.92196806626574</v>
       </c>
       <c r="F53">
-        <v>-1.416794192788628</v>
+        <v>-2.138033809588491</v>
       </c>
       <c r="G53">
-        <v>-4.739321865414798</v>
+        <v>-5.837893297166548</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.871463970959957</v>
       </c>
       <c r="E54">
-        <v>-14.30812326660279</v>
+        <v>-18.02537549748709</v>
       </c>
       <c r="F54">
-        <v>-1.780531976092697</v>
+        <v>-2.145823776644417</v>
       </c>
       <c r="G54">
-        <v>-4.997203431287406</v>
+        <v>-6.743718146530852</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.952954779028165</v>
       </c>
       <c r="E55">
-        <v>-14.54320993776298</v>
+        <v>-17.42873999002851</v>
       </c>
       <c r="F55">
-        <v>-1.662642869163285</v>
+        <v>-2.0919061707636</v>
       </c>
       <c r="G55">
-        <v>-4.928883702993466</v>
+        <v>-7.217549908475658</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.042524153698061</v>
       </c>
       <c r="E56">
-        <v>-14.06068291834967</v>
+        <v>-17.6365516622405</v>
       </c>
       <c r="F56">
-        <v>-1.715400760680183</v>
+        <v>-2.356070050414154</v>
       </c>
       <c r="G56">
-        <v>-4.868264303623871</v>
+        <v>-6.259514445411509</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.145346767634305</v>
       </c>
       <c r="E57">
-        <v>-13.85708272696481</v>
+        <v>-16.85507743121083</v>
       </c>
       <c r="F57">
-        <v>-1.398802881167226</v>
+        <v>-2.23682490604636</v>
       </c>
       <c r="G57">
-        <v>-5.511705245182158</v>
+        <v>-6.223244108483254</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.262119053364229</v>
       </c>
       <c r="E58">
-        <v>-12.90085015550514</v>
+        <v>-17.13292195395145</v>
       </c>
       <c r="F58">
-        <v>-1.640313397453422</v>
+        <v>-2.093404687395264</v>
       </c>
       <c r="G58">
-        <v>-5.205489714436191</v>
+        <v>-6.830457750205296</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.391337807782802</v>
       </c>
       <c r="E59">
-        <v>-13.60719247427355</v>
+        <v>-16.54304292971231</v>
       </c>
       <c r="F59">
-        <v>-1.892166080763569</v>
+        <v>-2.218034219881256</v>
       </c>
       <c r="G59">
-        <v>-5.074557638358016</v>
+        <v>-6.573132355983287</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.526493069104468</v>
       </c>
       <c r="E60">
-        <v>-12.41899787871897</v>
+        <v>-16.86363624708533</v>
       </c>
       <c r="F60">
-        <v>-1.786959278771018</v>
+        <v>-2.25241892240406</v>
       </c>
       <c r="G60">
-        <v>-5.901406113337466</v>
+        <v>-7.867141843645912</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.661519144312068</v>
       </c>
       <c r="E61">
-        <v>-12.62501174674992</v>
+        <v>-16.88155994720769</v>
       </c>
       <c r="F61">
-        <v>-1.723120316506871</v>
+        <v>-2.401114184676183</v>
       </c>
       <c r="G61">
-        <v>-5.830914667169765</v>
+        <v>-8.088739830408107</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.786535928874364</v>
       </c>
       <c r="E62">
-        <v>-12.73784773359904</v>
+        <v>-16.56406410605591</v>
       </c>
       <c r="F62">
-        <v>-1.830062548208288</v>
+        <v>-2.588799872230675</v>
       </c>
       <c r="G62">
-        <v>-5.887369400250956</v>
+        <v>-7.997163519700788</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.89566125933226</v>
       </c>
       <c r="E63">
-        <v>-12.61993079891332</v>
+        <v>-16.1529103654775</v>
       </c>
       <c r="F63">
-        <v>-2.047614194103313</v>
+        <v>-2.543681184902395</v>
       </c>
       <c r="G63">
-        <v>-6.07154498023723</v>
+        <v>-7.877705794461725</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.98124357914867</v>
       </c>
       <c r="E64">
-        <v>-11.85426547064443</v>
+        <v>-16.41369159815721</v>
       </c>
       <c r="F64">
-        <v>-2.037794726910528</v>
+        <v>-2.342709312574401</v>
       </c>
       <c r="G64">
-        <v>-6.368779000935154</v>
+        <v>-8.017341294762645</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.04285506449265</v>
       </c>
       <c r="E65">
-        <v>-12.06904646435422</v>
+        <v>-16.11968495168322</v>
       </c>
       <c r="F65">
-        <v>-1.995915784494596</v>
+        <v>-2.499868004600926</v>
       </c>
       <c r="G65">
-        <v>-6.188638975961252</v>
+        <v>-7.724440778175627</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.078046249390936</v>
       </c>
       <c r="E66">
-        <v>-12.67662729348935</v>
+        <v>-15.83950826482866</v>
       </c>
       <c r="F66">
-        <v>-1.637984856684152</v>
+        <v>-2.532301073522735</v>
       </c>
       <c r="G66">
-        <v>-6.200153053346837</v>
+        <v>-8.029798877626924</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.092000249570492</v>
       </c>
       <c r="E67">
-        <v>-12.27353423664459</v>
+        <v>-15.7582991404491</v>
       </c>
       <c r="F67">
-        <v>-2.097109146420584</v>
+        <v>-2.464342640164466</v>
       </c>
       <c r="G67">
-        <v>-6.317958816361802</v>
+        <v>-8.265201839287879</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.085728573951183</v>
       </c>
       <c r="E68">
-        <v>-11.31100255784025</v>
+        <v>-15.91268840479261</v>
       </c>
       <c r="F68">
-        <v>-2.031421268113389</v>
+        <v>-2.887399813183007</v>
       </c>
       <c r="G68">
-        <v>-6.750607391798075</v>
+        <v>-8.23689998547265</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.068395705345941</v>
       </c>
       <c r="E69">
-        <v>-11.84384545195278</v>
+        <v>-15.69917085533095</v>
       </c>
       <c r="F69">
-        <v>-2.344764492100746</v>
+        <v>-2.780548701895899</v>
       </c>
       <c r="G69">
-        <v>-6.549048137185088</v>
+        <v>-8.536779132056452</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.044000090348836</v>
       </c>
       <c r="E70">
-        <v>-12.11202168268702</v>
+        <v>-15.72878254686711</v>
       </c>
       <c r="F70">
-        <v>-2.390112637199603</v>
+        <v>-2.998195610042247</v>
       </c>
       <c r="G70">
-        <v>-6.461676219312643</v>
+        <v>-8.237264145481969</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.025345634311177</v>
       </c>
       <c r="E71">
-        <v>-11.59858782817136</v>
+        <v>-15.7153148651683</v>
       </c>
       <c r="F71">
-        <v>-2.446602323866112</v>
+        <v>-2.619303673471364</v>
       </c>
       <c r="G71">
-        <v>-6.141493496936491</v>
+        <v>-8.503428696293835</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.017294304924204</v>
       </c>
       <c r="E72">
-        <v>-12.23323534645033</v>
+        <v>-15.79471259994478</v>
       </c>
       <c r="F72">
-        <v>-2.408905808466915</v>
+        <v>-3.182630783908154</v>
       </c>
       <c r="G72">
-        <v>-7.21408707784158</v>
+        <v>-8.347220605023322</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.032492367555892</v>
       </c>
       <c r="E73">
-        <v>-12.2443210508211</v>
+        <v>-16.30974047731114</v>
       </c>
       <c r="F73">
-        <v>-2.493662704386555</v>
+        <v>-2.706955713463788</v>
       </c>
       <c r="G73">
-        <v>-6.567004536190096</v>
+        <v>-8.051363771269735</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.071276228574223</v>
       </c>
       <c r="E74">
-        <v>-12.24901254989305</v>
+        <v>-16.55379352700652</v>
       </c>
       <c r="F74">
-        <v>-2.578238187844982</v>
+        <v>-3.194815240035932</v>
       </c>
       <c r="G74">
-        <v>-5.897065988135481</v>
+        <v>-8.254869626659813</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.139989358734599</v>
       </c>
       <c r="E75">
-        <v>-12.81697375993507</v>
+        <v>-15.97031776501422</v>
       </c>
       <c r="F75">
-        <v>-2.620569418862842</v>
+        <v>-3.197905050448374</v>
       </c>
       <c r="G75">
-        <v>-6.498760950443559</v>
+        <v>-8.22386636768454</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.229938201311987</v>
       </c>
       <c r="E76">
-        <v>-12.8491078114935</v>
+        <v>-16.80011081370573</v>
       </c>
       <c r="F76">
-        <v>-3.150258185806749</v>
+        <v>-3.326765883627865</v>
       </c>
       <c r="G76">
-        <v>-6.242124149693717</v>
+        <v>-7.83980335858261</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.338582349542209</v>
       </c>
       <c r="E77">
-        <v>-13.4938130705435</v>
+        <v>-17.17011431097644</v>
       </c>
       <c r="F77">
-        <v>-2.611121060266511</v>
+        <v>-3.11828071895648</v>
       </c>
       <c r="G77">
-        <v>-5.558033019458719</v>
+        <v>-7.669839950596427</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.448367283660656</v>
       </c>
       <c r="E78">
-        <v>-13.97362753402622</v>
+        <v>-17.44328092006714</v>
       </c>
       <c r="F78">
-        <v>-2.950471707232162</v>
+        <v>-3.041414850915908</v>
       </c>
       <c r="G78">
-        <v>-6.081258120849452</v>
+        <v>-7.728482954279077</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.55160025687858</v>
       </c>
       <c r="E79">
-        <v>-13.46174694609519</v>
+        <v>-18.32461253143994</v>
       </c>
       <c r="F79">
-        <v>-3.10203312071797</v>
+        <v>-3.525157391496138</v>
       </c>
       <c r="G79">
-        <v>-5.542506560879538</v>
+        <v>-7.550289530082266</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.630035671128554</v>
       </c>
       <c r="E80">
-        <v>-15.09189796242835</v>
+        <v>-18.63535188937227</v>
       </c>
       <c r="F80">
-        <v>-2.989565678439881</v>
+        <v>-3.326364125437507</v>
       </c>
       <c r="G80">
-        <v>-5.542655535428804</v>
+        <v>-7.520408546044805</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.680195514952638</v>
       </c>
       <c r="E81">
-        <v>-15.5759284352122</v>
+        <v>-19.07822759037442</v>
       </c>
       <c r="F81">
-        <v>-3.051143197694385</v>
+        <v>-3.554010256503048</v>
       </c>
       <c r="G81">
-        <v>-5.314019328850119</v>
+        <v>-6.957758157826891</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.689354077384696</v>
       </c>
       <c r="E82">
-        <v>-16.07419643027617</v>
+        <v>-19.48356224185298</v>
       </c>
       <c r="F82">
-        <v>-2.978032319090704</v>
+        <v>-3.184413430558978</v>
       </c>
       <c r="G82">
-        <v>-5.111417252392261</v>
+        <v>-7.493884455184164</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.660370499099582</v>
       </c>
       <c r="E83">
-        <v>-16.30374024925097</v>
+        <v>-20.05482923792059</v>
       </c>
       <c r="F83">
-        <v>-2.992513009659042</v>
+        <v>-3.369475678548805</v>
       </c>
       <c r="G83">
-        <v>-4.969434575303999</v>
+        <v>-7.150249828207815</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.587051148859341</v>
       </c>
       <c r="E84">
-        <v>-17.19887012092515</v>
+        <v>-21.67493609890474</v>
       </c>
       <c r="F84">
-        <v>-3.145645007740559</v>
+        <v>-3.509903834140988</v>
       </c>
       <c r="G84">
-        <v>-4.763343183847749</v>
+        <v>-7.351418438447167</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.478866972019778</v>
       </c>
       <c r="E85">
-        <v>-18.38943310838573</v>
+        <v>-22.23470982794089</v>
       </c>
       <c r="F85">
-        <v>-3.237333682086825</v>
+        <v>-3.349758049259968</v>
       </c>
       <c r="G85">
-        <v>-4.585888011306196</v>
+        <v>-7.035082569987648</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.334620488604651</v>
       </c>
       <c r="E86">
-        <v>-19.75000406704228</v>
+        <v>-22.72932787295468</v>
       </c>
       <c r="F86">
-        <v>-3.339701668989982</v>
+        <v>-3.615110636133539</v>
       </c>
       <c r="G86">
-        <v>-4.72100792749155</v>
+        <v>-7.273902014645133</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.167663506891363</v>
       </c>
       <c r="E87">
-        <v>-20.29230694335683</v>
+        <v>-24.16201930865738</v>
       </c>
       <c r="F87">
-        <v>-3.506286353692963</v>
+        <v>-3.761753203981525</v>
       </c>
       <c r="G87">
-        <v>-4.445640060080511</v>
+        <v>-7.197653529784638</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.978816577581266</v>
       </c>
       <c r="E88">
-        <v>-21.92648830155682</v>
+        <v>-25.22886438622841</v>
       </c>
       <c r="F88">
-        <v>-3.111668690347334</v>
+        <v>-3.665288991558119</v>
       </c>
       <c r="G88">
-        <v>-4.85636951350127</v>
+        <v>-6.931485668427235</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.78262769236813</v>
       </c>
       <c r="E89">
-        <v>-22.81812219129707</v>
+        <v>-26.01315985656485</v>
       </c>
       <c r="F89">
-        <v>-3.619866293393011</v>
+        <v>-3.914037782209977</v>
       </c>
       <c r="G89">
-        <v>-4.224637971515385</v>
+        <v>-6.659074118182766</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.578482875523843</v>
       </c>
       <c r="E90">
-        <v>-24.16695081685173</v>
+        <v>-27.69892959066022</v>
       </c>
       <c r="F90">
-        <v>-3.501844647679152</v>
+        <v>-3.691895324168637</v>
       </c>
       <c r="G90">
-        <v>-4.543599102587546</v>
+        <v>-7.163389383453182</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.378285950505372</v>
       </c>
       <c r="E91">
-        <v>-25.77443229230249</v>
+        <v>-28.54344923682467</v>
       </c>
       <c r="F91">
-        <v>-3.404228176198453</v>
+        <v>-3.695143352755013</v>
       </c>
       <c r="G91">
-        <v>-4.624846511212339</v>
+        <v>-7.335958190778771</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.177471481120032</v>
       </c>
       <c r="E92">
-        <v>-27.37094127523267</v>
+        <v>-29.92045402765505</v>
       </c>
       <c r="F92">
-        <v>-3.68699635934848</v>
+        <v>-3.991495932943551</v>
       </c>
       <c r="G92">
-        <v>-4.211428894813693</v>
+        <v>-7.086389404755273</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.984852189855697</v>
       </c>
       <c r="E93">
-        <v>-28.75562635798006</v>
+        <v>-31.5604612676659</v>
       </c>
       <c r="F93">
-        <v>-3.55424468447804</v>
+        <v>-3.86995869597221</v>
       </c>
       <c r="G93">
-        <v>-4.645944617934115</v>
+        <v>-7.244405053890226</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.793609311470223</v>
       </c>
       <c r="E94">
-        <v>-30.80957461432105</v>
+        <v>-33.94234123350935</v>
       </c>
       <c r="F94">
-        <v>-3.671117384604217</v>
+        <v>-3.893619354098373</v>
       </c>
       <c r="G94">
-        <v>-5.007413153730518</v>
+        <v>-7.349888966408024</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.61189004424797</v>
       </c>
       <c r="E95">
-        <v>-32.84749660114889</v>
+        <v>-36.16440003043709</v>
       </c>
       <c r="F95">
-        <v>-3.784104213243861</v>
+        <v>-4.019170031136277</v>
       </c>
       <c r="G95">
-        <v>-5.838730865187984</v>
+        <v>-7.706325472984735</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.434425196890419</v>
       </c>
       <c r="E96">
-        <v>-34.98461933958876</v>
+        <v>-37.95325821108006</v>
       </c>
       <c r="F96">
-        <v>-4.040518715841226</v>
+        <v>-4.104306319326398</v>
       </c>
       <c r="G96">
-        <v>-5.087233717227885</v>
+        <v>-7.447679171092556</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.269708172053569</v>
       </c>
       <c r="E97">
-        <v>-37.56771751948903</v>
+        <v>-39.74410439181241</v>
       </c>
       <c r="F97">
-        <v>-3.893907625954546</v>
+        <v>-4.127480725787118</v>
       </c>
       <c r="G97">
-        <v>-5.798961281624719</v>
+        <v>-8.355324820503458</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.117801565876936</v>
       </c>
       <c r="E98">
-        <v>-39.12733981738973</v>
+        <v>-42.07355821406905</v>
       </c>
       <c r="F98">
-        <v>-4.103449787431904</v>
+        <v>-3.801045983365916</v>
       </c>
       <c r="G98">
-        <v>-5.80050068530048</v>
+        <v>-7.98575206922692</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.988886001989607</v>
       </c>
       <c r="E99">
-        <v>-40.59825157371717</v>
+        <v>-43.74613650338008</v>
       </c>
       <c r="F99">
-        <v>-4.244356739382906</v>
+        <v>-4.156018811180964</v>
       </c>
       <c r="G99">
-        <v>-6.792108390678379</v>
+        <v>-8.641938611111401</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.891544214995965</v>
       </c>
       <c r="E100">
-        <v>-43.82796376446168</v>
+        <v>-45.75923565993487</v>
       </c>
       <c r="F100">
-        <v>-4.223717965542156</v>
+        <v>-4.058570498283032</v>
       </c>
       <c r="G100">
-        <v>-6.674382080756357</v>
+        <v>-8.20664822033479</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.83152703675427</v>
       </c>
       <c r="E101">
-        <v>-46.09486803948737</v>
+        <v>-48.09116429323671</v>
       </c>
       <c r="F101">
-        <v>-4.101777313645652</v>
+        <v>-4.337841314258441</v>
       </c>
       <c r="G101">
-        <v>-7.43893602032334</v>
+        <v>-8.864298023347629</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.829158728382962</v>
       </c>
       <c r="E102">
-        <v>-48.26084621430412</v>
+        <v>-50.27356950751629</v>
       </c>
       <c r="F102">
-        <v>-4.352634299337635</v>
+        <v>-4.329056477951752</v>
       </c>
       <c r="G102">
-        <v>-7.610107777431358</v>
+        <v>-9.084283774432199</v>
       </c>
     </row>
   </sheetData>
